--- a/data/trans_dic/IP19C04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela</t>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,84</t>
+          <t>2,65; 12,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 11,81</t>
+          <t>1,82; 10,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,36</t>
+          <t>1,06; 10,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 13,82</t>
+          <t>3,31; 13,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 13,33</t>
+          <t>3,31; 13,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 18,85</t>
+          <t>5,95; 18,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,91</t>
+          <t>0,45; 6,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,75</t>
+          <t>3,57; 10,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,06</t>
+          <t>4,85; 12,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,91</t>
+          <t>1,18; 6,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,85</t>
+          <t>1,96; 7,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,83</t>
+          <t>3,34; 10,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,1</t>
+          <t>3,99; 11,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,15</t>
+          <t>3,42; 11,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 12,15</t>
+          <t>2,58; 11,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 13,19</t>
+          <t>4,44; 12,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,85</t>
+          <t>1,1; 6,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,9</t>
+          <t>2,55; 10,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,35</t>
+          <t>1,1; 6,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,39</t>
+          <t>4,84; 10,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,0</t>
+          <t>3,11; 7,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,09</t>
+          <t>3,69; 9,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,06</t>
+          <t>2,38; 7,38</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,31</t>
+          <t>0,92; 8,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 16,21</t>
+          <t>5,06; 15,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,54</t>
+          <t>1,49; 8,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,35</t>
+          <t>2,1; 9,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,38</t>
+          <t>4,59; 15,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 13,15</t>
+          <t>2,99; 13,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,06</t>
+          <t>0,85; 8,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,21</t>
+          <t>1,75; 9,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 10,51</t>
+          <t>3,77; 10,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 12,19</t>
+          <t>5,32; 12,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,32</t>
+          <t>1,99; 6,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,58</t>
+          <t>2,52; 7,55</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 11,59</t>
+          <t>3,23; 11,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,31</t>
+          <t>1,06; 8,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,72</t>
+          <t>2,45; 10,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,07</t>
+          <t>0,55; 5,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,22</t>
+          <t>1,62; 9,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,66</t>
+          <t>1,34; 8,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,7</t>
+          <t>1,77; 8,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,8</t>
+          <t>1,18; 7,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,92</t>
+          <t>3,17; 8,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,02</t>
+          <t>1,76; 7,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,89</t>
+          <t>2,67; 8,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,11</t>
+          <t>1,34; 4,95</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,19</t>
+          <t>4,02; 8,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,81</t>
+          <t>4,48; 8,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,5</t>
+          <t>3,6; 7,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,17</t>
+          <t>2,89; 7,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,5</t>
+          <t>5,28; 9,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,9</t>
+          <t>4,14; 7,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,99</t>
+          <t>2,45; 5,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,03</t>
+          <t>2,04; 4,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,06</t>
+          <t>5,13; 8,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,69</t>
+          <t>4,65; 7,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,05</t>
+          <t>3,47; 6,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,22</t>
+          <t>2,88; 5,21</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4864</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3116</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4633</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8434</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>10582</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12141</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4543</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6404</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2003; 9276</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1349; 7738</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>750; 7591</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2311; 9154</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2724; 10767</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4478; 14163</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4709</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>385; 5196</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5636; 16606</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7235; 18928</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1727; 9332</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3035; 11592</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6882</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6986</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6513</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8775</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>15657</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11378</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12959</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>11442</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3673; 11842</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4498; 13506</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3666; 12036</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2940; 13367</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4951; 14155</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1263; 7158</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2772; 11551</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1838; 10569</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10725; 23000</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7077; 17719</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7964; 19642</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>6697; 20753</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2552</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7151</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2959</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5368</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7032</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2785</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5152</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9585</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12545</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5744</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10520</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>638; 5717</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3770; 11808</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1130; 6721</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2244; 10614</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3573; 11688</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2384; 10445</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>653; 6782</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2105; 11415</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5538; 14856</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8202; 19984</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3027; 10354</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5737; 17156</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6221</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3253</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6119</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4094</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4261</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3758</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>10315</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7133</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10380</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5623</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3104; 11513</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>985; 8198</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2681; 11658</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>559; 5700</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1460; 8353</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1295; 8542</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1896; 8846</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1322; 8358</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>5890; 16663</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3333; 13489</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5786; 17433</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2857; 10542</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20519</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22220</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19181</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18379</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15609</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>46138</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>43199</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33626</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>33988</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>14119; 28552</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15861; 31414</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13070; 26731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11319; 27500</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19093; 35073</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15142; 29179</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9018; 21743</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9892; 23604</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>36529; 58819</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>33459; 55034</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>25371; 44038</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>25192; 45601</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 12,26</t>
+          <t>2,8; 12,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,47</t>
+          <t>1,85; 10,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,72</t>
+          <t>1,01; 10,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 13,12</t>
+          <t>3,0; 13,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 13,1</t>
+          <t>3,28; 13,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 18,82</t>
+          <t>5,81; 19,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>0,0; 6,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,09</t>
+          <t>0,44; 6,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 10,52</t>
+          <t>3,91; 10,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 12,69</t>
+          <t>4,9; 12,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,36</t>
+          <t>1,34; 6,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,48</t>
+          <t>2,03; 7,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,76</t>
+          <t>3,2; 10,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 11,99</t>
+          <t>4,08; 11,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,23</t>
+          <t>3,42; 11,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 11,75</t>
+          <t>2,81; 12,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,68</t>
+          <t>4,25; 12,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,24</t>
+          <t>1,08; 6,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,64</t>
+          <t>2,63; 10,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,31</t>
+          <t>0,98; 6,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 10,37</t>
+          <t>4,69; 10,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,8</t>
+          <t>2,92; 7,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,1</t>
+          <t>3,58; 8,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,38</t>
+          <t>2,32; 6,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,26</t>
+          <t>0,94; 9,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 15,85</t>
+          <t>5,42; 16,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,89</t>
+          <t>1,51; 9,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,92</t>
+          <t>2,03; 9,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 15,01</t>
+          <t>4,9; 15,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 13,1</t>
+          <t>2,97; 12,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,82</t>
+          <t>0,85; 8,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 9,49</t>
+          <t>1,62; 8,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,1</t>
+          <t>3,93; 10,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,96</t>
+          <t>5,07; 12,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,79</t>
+          <t>1,71; 7,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,55</t>
+          <t>2,43; 7,71</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,99</t>
+          <t>3,06; 12,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,82</t>
+          <t>0,86; 8,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 10,64</t>
+          <t>2,61; 10,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,63</t>
+          <t>0,56; 5,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,28</t>
+          <t>2,09; 9,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,87</t>
+          <t>1,41; 9,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 8,24</t>
+          <t>1,83; 8,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,49</t>
+          <t>1,25; 7,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,96</t>
+          <t>3,24; 9,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,13</t>
+          <t>1,89; 7,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 8,03</t>
+          <t>2,77; 7,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,95</t>
+          <t>1,3; 4,97</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,14</t>
+          <t>3,95; 8,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,87</t>
+          <t>4,42; 8,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,36</t>
+          <t>3,68; 7,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,02</t>
+          <t>3,14; 6,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,7</t>
+          <t>5,1; 9,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,97</t>
+          <t>3,91; 8,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,9</t>
+          <t>2,51; 5,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,87</t>
+          <t>2,0; 4,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,25</t>
+          <t>5,0; 7,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,64</t>
+          <t>4,66; 7,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,02</t>
+          <t>3,53; 5,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,21</t>
+          <t>2,77; 5,19</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2003; 9276</t>
+          <t>2122; 9230</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1349; 7738</t>
+          <t>1365; 7985</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>750; 7591</t>
+          <t>715; 7679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2311; 9154</t>
+          <t>2093; 9179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2724; 10767</t>
+          <t>2695; 10993</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4478; 14163</t>
+          <t>4368; 14543</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4709</t>
+          <t>0; 5150</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>385; 5196</t>
+          <t>373; 5641</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5636; 16606</t>
+          <t>6179; 16364</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7235; 18928</t>
+          <t>7304; 19324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1727; 9332</t>
+          <t>1966; 10106</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3035; 11592</t>
+          <t>3153; 11853</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3673; 11842</t>
+          <t>3522; 11488</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4498; 13506</t>
+          <t>4592; 12934</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3666; 12036</t>
+          <t>3661; 11809</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2940; 13367</t>
+          <t>3193; 13951</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4951; 14155</t>
+          <t>4748; 14200</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1263; 7158</t>
+          <t>1242; 7228</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2772; 11551</t>
+          <t>2854; 11305</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1838; 10569</t>
+          <t>1649; 10098</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10725; 23000</t>
+          <t>10388; 22357</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7077; 17719</t>
+          <t>6645; 17275</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7964; 19642</t>
+          <t>7719; 19153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6697; 20753</t>
+          <t>6525; 19481</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>638; 5717</t>
+          <t>648; 6368</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3770; 11808</t>
+          <t>4035; 12168</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1130; 6721</t>
+          <t>1140; 6978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2244; 10614</t>
+          <t>2170; 9840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3573; 11688</t>
+          <t>3816; 11803</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2384; 10445</t>
+          <t>2371; 9572</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>653; 6782</t>
+          <t>656; 6872</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2105; 11415</t>
+          <t>1949; 10718</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5538; 14856</t>
+          <t>5774; 14983</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8202; 19984</t>
+          <t>7825; 19346</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3027; 10354</t>
+          <t>2601; 10760</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5737; 17156</t>
+          <t>5527; 17523</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3104; 11513</t>
+          <t>2941; 11592</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>985; 8198</t>
+          <t>797; 7764</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2681; 11658</t>
+          <t>2859; 11780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>559; 5700</t>
+          <t>567; 5580</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1460; 8353</t>
+          <t>1881; 8264</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1295; 8542</t>
+          <t>1357; 8879</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1896; 8846</t>
+          <t>1961; 8753</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1322; 8358</t>
+          <t>1400; 7818</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5890; 16663</t>
+          <t>6030; 16862</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3333; 13489</t>
+          <t>3582; 13517</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5786; 17433</t>
+          <t>6000; 17120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2857; 10542</t>
+          <t>2769; 10566</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14119; 28552</t>
+          <t>13855; 28870</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15861; 31414</t>
+          <t>15659; 31640</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13070; 26731</t>
+          <t>13357; 27656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11319; 27500</t>
+          <t>12298; 27037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19093; 35073</t>
+          <t>18465; 34049</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15142; 29179</t>
+          <t>14294; 29573</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9018; 21743</t>
+          <t>9254; 21615</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9892; 23604</t>
+          <t>9669; 23862</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36529; 58819</t>
+          <t>35600; 56580</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33459; 55034</t>
+          <t>33571; 54266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25371; 44038</t>
+          <t>25839; 43764</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25192; 45601</t>
+          <t>24239; 45443</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,2</t>
+          <t>3,44; 13,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,8</t>
+          <t>5,94; 18,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,84</t>
+          <t>0,0; 6,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 13,16</t>
+          <t>0,45; 5,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 13,37</t>
+          <t>2,6; 11,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 19,33</t>
+          <t>1,88; 11,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,79</t>
+          <t>1,08; 10,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,62</t>
+          <t>2,61; 13,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,37</t>
+          <t>3,99; 10,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,96</t>
+          <t>4,96; 13,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,89</t>
+          <t>1,18; 6,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,65</t>
+          <t>2,03; 7,72</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>6,52%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 10,44</t>
+          <t>4,3; 13,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 11,49</t>
+          <t>1,12; 5,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,02</t>
+          <t>2,65; 9,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,27</t>
+          <t>1,15; 6,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,72</t>
+          <t>3,16; 10,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,3</t>
+          <t>3,68; 12,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 10,41</t>
+          <t>3,21; 11,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,03</t>
+          <t>1,97; 7,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,08</t>
+          <t>4,61; 10,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,6</t>
+          <t>3,0; 8,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,88</t>
+          <t>3,66; 9,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,93</t>
+          <t>1,88; 5,79</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,6%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,2</t>
+          <t>4,83; 15,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 16,33</t>
+          <t>2,93; 13,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,23</t>
+          <t>1,15; 9,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,2</t>
+          <t>1,83; 10,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 15,16</t>
+          <t>0,94; 9,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 12,0</t>
+          <t>5,08; 16,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,94</t>
+          <t>1,48; 8,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,91</t>
+          <t>2,44; 10,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,19</t>
+          <t>3,82; 10,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,54</t>
+          <t>5,15; 12,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,06</t>
+          <t>1,98; 7,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,71</t>
+          <t>2,53; 7,99</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,58%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 12,08</t>
+          <t>2,09; 9,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,35</t>
+          <t>1,4; 8,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 10,75</t>
+          <t>1,44; 8,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,51</t>
+          <t>1,16; 7,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,18</t>
+          <t>3,22; 11,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,22</t>
+          <t>0,83; 8,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,15</t>
+          <t>2,53; 10,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,01</t>
+          <t>0,48; 4,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,06</t>
+          <t>3,13; 8,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,14</t>
+          <t>1,72; 7,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,89</t>
+          <t>2,91; 7,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,97</t>
+          <t>1,12; 4,84</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,23</t>
+          <t>5,24; 9,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,94</t>
+          <t>3,98; 7,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,61</t>
+          <t>2,4; 5,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,9</t>
+          <t>1,93; 4,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,41</t>
+          <t>4,11; 8,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,08</t>
+          <t>4,5; 8,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,86</t>
+          <t>3,59; 7,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,93</t>
+          <t>2,91; 6,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,94</t>
+          <t>5,12; 8,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,54</t>
+          <t>4,6; 7,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,98</t>
+          <t>3,41; 6,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,19</t>
+          <t>2,65; 5,01</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8434</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4864</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3707</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3116</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5718</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8434</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>6382</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2122; 9230</t>
+          <t>2829; 10960</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1365; 7985</t>
+          <t>4467; 14186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>715; 7679</t>
+          <t>0; 4574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2093; 9179</t>
+          <t>366; 4506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2695; 10993</t>
+          <t>1965; 8957</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4368; 14543</t>
+          <t>1389; 8730</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5150</t>
+          <t>764; 7339</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>373; 5641</t>
+          <t>1938; 10108</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6179; 16364</t>
+          <t>6302; 16963</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7304; 19324</t>
+          <t>7400; 19487</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1966; 10106</t>
+          <t>1736; 10132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3153; 11853</t>
+          <t>3161; 12022</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8775</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4727</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6882</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8109</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6986</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6513</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8775</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5972</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>9552</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3522; 11488</t>
+          <t>4798; 14727</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4592; 12934</t>
+          <t>1283; 6706</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3661; 11809</t>
+          <t>2875; 10754</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3193; 13951</t>
+          <t>1868; 10348</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4748; 14200</t>
+          <t>3477; 11920</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1242; 7228</t>
+          <t>4143; 13619</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2854; 11305</t>
+          <t>3438; 11952</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1649; 10098</t>
+          <t>2305; 8822</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10388; 22357</t>
+          <t>10217; 23037</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6645; 17275</t>
+          <t>6816; 18184</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7719; 19153</t>
+          <t>7902; 19614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6525; 19481</t>
+          <t>5240; 16162</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7032</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2785</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4833</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2552</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7151</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2959</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5368</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7032</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10550</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>648; 6368</t>
+          <t>3761; 11974</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4035; 12168</t>
+          <t>2335; 10486</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1140; 6978</t>
+          <t>881; 6962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2170; 9840</t>
+          <t>2057; 11500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3816; 11803</t>
+          <t>652; 6443</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2371; 9572</t>
+          <t>3785; 12074</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>656; 6872</t>
+          <t>1122; 6454</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1949; 10718</t>
+          <t>2498; 11056</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5774; 14983</t>
+          <t>5618; 15454</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7825; 19346</t>
+          <t>7942; 18798</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2601; 10760</t>
+          <t>3025; 11157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5527; 17523</t>
+          <t>5421; 17144</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4094</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4261</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6221</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3253</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6119</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4094</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3881</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4261</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5172</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2941; 11592</t>
+          <t>1886; 8305</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>797; 7764</t>
+          <t>1350; 8340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2859; 11780</t>
+          <t>1546; 9348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>567; 5580</t>
+          <t>1222; 7811</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1881; 8264</t>
+          <t>3093; 11126</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1357; 8879</t>
+          <t>769; 7723</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1961; 8753</t>
+          <t>2775; 11743</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1400; 7818</t>
+          <t>491; 4948</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6030; 16862</t>
+          <t>5814; 16586</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3582; 13517</t>
+          <t>3264; 13285</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6000; 17120</t>
+          <t>6307; 17126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2769; 10566</t>
+          <t>2319; 10055</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14433</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>20519</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>22220</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>19181</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18379</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25619</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20978</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>31657</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13855; 28870</t>
+          <t>18948; 34357</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15659; 31640</t>
+          <t>14563; 28916</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13357; 27656</t>
+          <t>8866; 22080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12298; 27037</t>
+          <t>8914; 22960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18465; 34049</t>
+          <t>14407; 28733</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14294; 29573</t>
+          <t>15946; 31191</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9254; 21615</t>
+          <t>13055; 27246</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9669; 23862</t>
+          <t>11527; 25018</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35600; 56580</t>
+          <t>36483; 57423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33571; 54266</t>
+          <t>33116; 55403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25839; 43764</t>
+          <t>24962; 44272</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24239; 45443</t>
+          <t>22739; 42952</t>
         </is>
       </c>
     </row>
